--- a/artfynd/A 28687-2024 artfynd.xlsx
+++ b/artfynd/A 28687-2024 artfynd.xlsx
@@ -2812,10 +2812,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119536281</v>
+        <v>119536991</v>
       </c>
       <c r="B21" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2824,25 +2824,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546344</v>
+        <v>546459</v>
       </c>
       <c r="R21" t="n">
-        <v>7207127</v>
+        <v>7206834</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3036,10 +3036,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119536991</v>
+        <v>119536281</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3048,25 +3048,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3076,10 +3076,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>546459</v>
+        <v>546344</v>
       </c>
       <c r="R23" t="n">
-        <v>7206834</v>
+        <v>7207127</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -5281,10 +5281,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119536977</v>
+        <v>119536364</v>
       </c>
       <c r="B43" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5297,21 +5297,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>546290</v>
+        <v>546248</v>
       </c>
       <c r="R43" t="n">
-        <v>7207241</v>
+        <v>7207265</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5393,7 +5393,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119536992</v>
+        <v>119536977</v>
       </c>
       <c r="B44" t="n">
         <v>78526</v>
@@ -5433,10 +5433,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>546442</v>
+        <v>546290</v>
       </c>
       <c r="R44" t="n">
-        <v>7206832</v>
+        <v>7207241</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5468,7 +5468,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5505,10 +5505,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119536364</v>
+        <v>119536992</v>
       </c>
       <c r="B45" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5521,21 +5521,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5545,10 +5545,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>546248</v>
+        <v>546442</v>
       </c>
       <c r="R45" t="n">
-        <v>7207265</v>
+        <v>7206832</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 28687-2024 artfynd.xlsx
+++ b/artfynd/A 28687-2024 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119536987</v>
+        <v>119537144</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>74630</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546333</v>
+        <v>546388</v>
       </c>
       <c r="R4" t="n">
-        <v>7207020</v>
+        <v>7206925</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119536989</v>
+        <v>119536795</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546388</v>
+        <v>546329</v>
       </c>
       <c r="R5" t="n">
-        <v>7206925</v>
+        <v>7207211</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119536984</v>
+        <v>119536987</v>
       </c>
       <c r="B6" t="n">
         <v>78526</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546325</v>
+        <v>546333</v>
       </c>
       <c r="R6" t="n">
-        <v>7207065</v>
+        <v>7207020</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119535973</v>
+        <v>119536989</v>
       </c>
       <c r="B7" t="n">
-        <v>74638</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546265</v>
+        <v>546388</v>
       </c>
       <c r="R7" t="n">
-        <v>7207255</v>
+        <v>7206925</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119537144</v>
+        <v>119536984</v>
       </c>
       <c r="B8" t="n">
-        <v>74630</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546388</v>
+        <v>546325</v>
       </c>
       <c r="R8" t="n">
-        <v>7206925</v>
+        <v>7207065</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119536795</v>
+        <v>119535973</v>
       </c>
       <c r="B9" t="n">
-        <v>90576</v>
+        <v>74638</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546329</v>
+        <v>546265</v>
       </c>
       <c r="R9" t="n">
-        <v>7207211</v>
+        <v>7207255</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -4044,10 +4044,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119536368</v>
+        <v>119536779</v>
       </c>
       <c r="B32" t="n">
-        <v>79608</v>
+        <v>74622</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4056,25 +4056,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4084,10 +4084,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>546348</v>
+        <v>546292</v>
       </c>
       <c r="R32" t="n">
-        <v>7207126</v>
+        <v>7207246</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4119,7 +4119,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4156,10 +4156,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119536779</v>
+        <v>119536368</v>
       </c>
       <c r="B33" t="n">
-        <v>74622</v>
+        <v>79608</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4168,25 +4168,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>546292</v>
+        <v>546348</v>
       </c>
       <c r="R33" t="n">
-        <v>7207246</v>
+        <v>7207126</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5281,10 +5281,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119536364</v>
+        <v>119536977</v>
       </c>
       <c r="B43" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5297,21 +5297,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>546248</v>
+        <v>546290</v>
       </c>
       <c r="R43" t="n">
-        <v>7207265</v>
+        <v>7207241</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5393,7 +5393,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119536977</v>
+        <v>119536992</v>
       </c>
       <c r="B44" t="n">
         <v>78526</v>
@@ -5433,10 +5433,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>546290</v>
+        <v>546442</v>
       </c>
       <c r="R44" t="n">
-        <v>7207241</v>
+        <v>7206832</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5468,7 +5468,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5505,10 +5505,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119536992</v>
+        <v>119536364</v>
       </c>
       <c r="B45" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5521,21 +5521,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5545,10 +5545,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>546442</v>
+        <v>546248</v>
       </c>
       <c r="R45" t="n">
-        <v>7206832</v>
+        <v>7207265</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 28687-2024 artfynd.xlsx
+++ b/artfynd/A 28687-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119536479</v>
+        <v>119537144</v>
       </c>
       <c r="B2" t="n">
-        <v>74643</v>
+        <v>74630</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1467</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546383</v>
+        <v>546388</v>
       </c>
       <c r="R2" t="n">
         <v>7206925</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119536477</v>
+        <v>119536987</v>
       </c>
       <c r="B3" t="n">
-        <v>74643</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546332</v>
+        <v>546333</v>
       </c>
       <c r="R3" t="n">
-        <v>7207014</v>
+        <v>7207020</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119537144</v>
+        <v>119535975</v>
       </c>
       <c r="B4" t="n">
-        <v>74630</v>
+        <v>74638</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546388</v>
+        <v>546362</v>
       </c>
       <c r="R4" t="n">
-        <v>7206925</v>
+        <v>7207136</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119536795</v>
+        <v>119536302</v>
       </c>
       <c r="B5" t="n">
-        <v>90576</v>
+        <v>77866</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>6443</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546329</v>
+        <v>546461</v>
       </c>
       <c r="R5" t="n">
-        <v>7207211</v>
+        <v>7206830</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119536987</v>
+        <v>119536475</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>74643</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546333</v>
+        <v>546250</v>
       </c>
       <c r="R6" t="n">
-        <v>7207020</v>
+        <v>7207262</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119536989</v>
+        <v>119536477</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>74643</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546388</v>
+        <v>546332</v>
       </c>
       <c r="R7" t="n">
-        <v>7206925</v>
+        <v>7207014</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119536984</v>
+        <v>119536975</v>
       </c>
       <c r="B8" t="n">
         <v>78526</v>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546325</v>
+        <v>546239</v>
       </c>
       <c r="R8" t="n">
-        <v>7207065</v>
+        <v>7207276</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119535973</v>
+        <v>119537038</v>
       </c>
       <c r="B9" t="n">
-        <v>74638</v>
+        <v>82305</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546265</v>
+        <v>546336</v>
       </c>
       <c r="R9" t="n">
-        <v>7207255</v>
+        <v>7207063</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119537039</v>
+        <v>119535976</v>
       </c>
       <c r="B10" t="n">
-        <v>82305</v>
+        <v>74638</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546421</v>
+        <v>546348</v>
       </c>
       <c r="R10" t="n">
-        <v>7206851</v>
+        <v>7207093</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119536986</v>
+        <v>119536047</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,34 +1699,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546326</v>
+        <v>546331</v>
       </c>
       <c r="R11" t="n">
-        <v>7207041</v>
+        <v>7207021</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119536975</v>
+        <v>119536622</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>94311</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,25 +1812,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546239</v>
+        <v>546344</v>
       </c>
       <c r="R12" t="n">
-        <v>7207276</v>
+        <v>7207094</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119537037</v>
+        <v>119537116</v>
       </c>
       <c r="B13" t="n">
-        <v>82305</v>
+        <v>86878</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1928,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546290</v>
+        <v>546360</v>
       </c>
       <c r="R13" t="n">
-        <v>7207239</v>
+        <v>7206982</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119535975</v>
+        <v>119536779</v>
       </c>
       <c r="B14" t="n">
-        <v>74638</v>
+        <v>74622</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,25 +2036,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546362</v>
+        <v>546292</v>
       </c>
       <c r="R14" t="n">
-        <v>7207136</v>
+        <v>7207246</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2094,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119536109</v>
+        <v>119536368</v>
       </c>
       <c r="B15" t="n">
-        <v>57463</v>
+        <v>79608</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,43 +2152,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546249</v>
+        <v>546348</v>
       </c>
       <c r="R15" t="n">
-        <v>7207263</v>
+        <v>7207126</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2215,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2225,7 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119537116</v>
+        <v>119536992</v>
       </c>
       <c r="B16" t="n">
-        <v>86878</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2268,21 +2264,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2292,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546360</v>
+        <v>546442</v>
       </c>
       <c r="R16" t="n">
-        <v>7206982</v>
+        <v>7206832</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2327,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2337,7 +2333,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,10 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119536622</v>
+        <v>119536990</v>
       </c>
       <c r="B17" t="n">
-        <v>94311</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2376,25 +2372,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2404,10 +2400,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546344</v>
+        <v>546421</v>
       </c>
       <c r="R17" t="n">
-        <v>7207094</v>
+        <v>7206848</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2439,7 +2435,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2449,7 +2445,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,10 +2472,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119536371</v>
+        <v>119535973</v>
       </c>
       <c r="B18" t="n">
-        <v>79608</v>
+        <v>74638</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2492,21 +2488,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2516,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546410</v>
+        <v>546265</v>
       </c>
       <c r="R18" t="n">
-        <v>7206846</v>
+        <v>7207255</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2551,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2561,7 +2557,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119536983</v>
+        <v>119536279</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2600,25 +2596,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2628,10 +2624,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>546349</v>
+        <v>546347</v>
       </c>
       <c r="R19" t="n">
-        <v>7207094</v>
+        <v>7207179</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2663,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2673,7 +2669,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2700,10 +2696,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119535976</v>
+        <v>119536700</v>
       </c>
       <c r="B20" t="n">
-        <v>74638</v>
+        <v>77463</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2716,21 +2712,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2740,10 +2736,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546348</v>
+        <v>546362</v>
       </c>
       <c r="R20" t="n">
-        <v>7207093</v>
+        <v>7207136</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2775,7 +2771,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2785,7 +2781,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2924,10 +2920,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119536475</v>
+        <v>119536979</v>
       </c>
       <c r="B22" t="n">
-        <v>74643</v>
+        <v>78526</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2940,21 +2936,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2964,10 +2960,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546250</v>
+        <v>546364</v>
       </c>
       <c r="R22" t="n">
-        <v>7207262</v>
+        <v>7207146</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2999,7 +2995,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3009,7 +3005,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3036,10 +3032,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119536281</v>
+        <v>119536983</v>
       </c>
       <c r="B23" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3048,25 +3044,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3076,10 +3072,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>546344</v>
+        <v>546349</v>
       </c>
       <c r="R23" t="n">
-        <v>7207127</v>
+        <v>7207094</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3111,7 +3107,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3121,7 +3117,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3148,10 +3144,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119536369</v>
+        <v>119536689</v>
       </c>
       <c r="B24" t="n">
-        <v>79608</v>
+        <v>79643</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3160,25 +3156,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3188,10 +3184,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>546326</v>
+        <v>546346</v>
       </c>
       <c r="R24" t="n">
-        <v>7207066</v>
+        <v>7207122</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3223,7 +3219,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3233,7 +3229,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3260,10 +3256,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119536365</v>
+        <v>119536281</v>
       </c>
       <c r="B25" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3272,25 +3268,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3300,10 +3296,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>546304</v>
+        <v>546344</v>
       </c>
       <c r="R25" t="n">
-        <v>7207242</v>
+        <v>7207127</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3335,7 +3331,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3345,7 +3341,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3484,10 +3480,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119536295</v>
+        <v>119536479</v>
       </c>
       <c r="B27" t="n">
-        <v>97928</v>
+        <v>74643</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3496,25 +3492,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221952</v>
+        <v>1467</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3524,10 +3520,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>546393</v>
+        <v>546383</v>
       </c>
       <c r="R27" t="n">
-        <v>7206921</v>
+        <v>7206925</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3559,7 +3555,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3569,7 +3565,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3596,10 +3592,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119536302</v>
+        <v>119536980</v>
       </c>
       <c r="B28" t="n">
-        <v>77866</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3608,25 +3604,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6443</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3636,10 +3632,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>546461</v>
+        <v>546362</v>
       </c>
       <c r="R28" t="n">
-        <v>7206830</v>
+        <v>7207137</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3671,7 +3667,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3681,7 +3677,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3708,10 +3704,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119536366</v>
+        <v>119536988</v>
       </c>
       <c r="B29" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3724,21 +3720,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3748,10 +3744,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>546346</v>
+        <v>546361</v>
       </c>
       <c r="R29" t="n">
-        <v>7207178</v>
+        <v>7206982</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3783,7 +3779,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3793,7 +3789,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3820,10 +3816,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119535974</v>
+        <v>119536367</v>
       </c>
       <c r="B30" t="n">
-        <v>74638</v>
+        <v>79608</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3836,21 +3832,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3860,10 +3856,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>546291</v>
+        <v>546365</v>
       </c>
       <c r="R30" t="n">
-        <v>7207241</v>
+        <v>7207145</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3895,7 +3891,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3905,7 +3901,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3932,10 +3928,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119536981</v>
+        <v>119536365</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3948,21 +3944,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3972,10 +3968,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>546348</v>
+        <v>546304</v>
       </c>
       <c r="R31" t="n">
-        <v>7207126</v>
+        <v>7207242</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4007,7 +4003,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4017,7 +4013,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4044,10 +4040,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119536779</v>
+        <v>119537037</v>
       </c>
       <c r="B32" t="n">
-        <v>74622</v>
+        <v>82305</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4056,25 +4052,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6439</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4084,10 +4080,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>546292</v>
+        <v>546290</v>
       </c>
       <c r="R32" t="n">
-        <v>7207246</v>
+        <v>7207239</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4119,7 +4115,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4129,7 +4125,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4156,10 +4152,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119536368</v>
+        <v>119536989</v>
       </c>
       <c r="B33" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4172,21 +4168,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4196,10 +4192,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>546348</v>
+        <v>546388</v>
       </c>
       <c r="R33" t="n">
-        <v>7207126</v>
+        <v>7206925</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4231,7 +4227,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4241,7 +4237,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4268,7 +4264,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119536980</v>
+        <v>119536978</v>
       </c>
       <c r="B34" t="n">
         <v>78526</v>
@@ -4308,10 +4304,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>546362</v>
+        <v>546304</v>
       </c>
       <c r="R34" t="n">
-        <v>7207137</v>
+        <v>7207241</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4343,7 +4339,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4353,7 +4349,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4380,10 +4376,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119536278</v>
+        <v>119536795</v>
       </c>
       <c r="B35" t="n">
-        <v>79636</v>
+        <v>90576</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4392,25 +4388,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4420,10 +4416,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>546304</v>
+        <v>546329</v>
       </c>
       <c r="R35" t="n">
-        <v>7207242</v>
+        <v>7207211</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4455,7 +4451,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4465,7 +4461,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4492,7 +4488,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119536979</v>
+        <v>119536977</v>
       </c>
       <c r="B36" t="n">
         <v>78526</v>
@@ -4532,10 +4528,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>546364</v>
+        <v>546290</v>
       </c>
       <c r="R36" t="n">
-        <v>7207146</v>
+        <v>7207241</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4567,7 +4563,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4577,7 +4573,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4604,10 +4600,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119537038</v>
+        <v>119536278</v>
       </c>
       <c r="B37" t="n">
-        <v>82305</v>
+        <v>79636</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4616,25 +4612,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4644,10 +4640,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>546336</v>
+        <v>546304</v>
       </c>
       <c r="R37" t="n">
-        <v>7207063</v>
+        <v>7207242</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4679,7 +4675,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4689,7 +4685,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4716,10 +4712,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119536523</v>
+        <v>119536976</v>
       </c>
       <c r="B38" t="n">
-        <v>96862</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4728,25 +4724,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4756,10 +4752,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>546346</v>
+        <v>546262</v>
       </c>
       <c r="R38" t="n">
-        <v>7207114</v>
+        <v>7207258</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4791,7 +4787,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4801,7 +4797,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4828,10 +4824,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119536976</v>
+        <v>119536371</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4844,21 +4840,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4868,10 +4864,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>546262</v>
+        <v>546410</v>
       </c>
       <c r="R39" t="n">
-        <v>7207258</v>
+        <v>7206846</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4903,7 +4899,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4913,7 +4909,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4940,10 +4936,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119536988</v>
+        <v>119535974</v>
       </c>
       <c r="B40" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4956,21 +4952,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4980,10 +4976,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>546361</v>
+        <v>546291</v>
       </c>
       <c r="R40" t="n">
-        <v>7206982</v>
+        <v>7207241</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5015,7 +5011,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5025,7 +5021,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5052,10 +5048,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119536047</v>
+        <v>119536109</v>
       </c>
       <c r="B41" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5068,27 +5064,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>546331</v>
+        <v>546249</v>
       </c>
       <c r="R41" t="n">
-        <v>7207021</v>
+        <v>7207263</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5169,10 +5169,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119536279</v>
+        <v>119536366</v>
       </c>
       <c r="B42" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5181,25 +5181,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5209,10 +5209,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>546347</v>
+        <v>546346</v>
       </c>
       <c r="R42" t="n">
-        <v>7207179</v>
+        <v>7207178</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5281,7 +5281,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119536977</v>
+        <v>119536984</v>
       </c>
       <c r="B43" t="n">
         <v>78526</v>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>546290</v>
+        <v>546325</v>
       </c>
       <c r="R43" t="n">
-        <v>7207241</v>
+        <v>7207065</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5393,7 +5393,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119536992</v>
+        <v>119536986</v>
       </c>
       <c r="B44" t="n">
         <v>78526</v>
@@ -5433,10 +5433,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>546442</v>
+        <v>546326</v>
       </c>
       <c r="R44" t="n">
-        <v>7206832</v>
+        <v>7207041</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5468,7 +5468,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5505,10 +5505,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119536364</v>
+        <v>119536295</v>
       </c>
       <c r="B45" t="n">
-        <v>79608</v>
+        <v>97928</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5517,25 +5517,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5545,10 +5545,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>546248</v>
+        <v>546393</v>
       </c>
       <c r="R45" t="n">
-        <v>7207265</v>
+        <v>7206921</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5617,10 +5617,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119536700</v>
+        <v>119537039</v>
       </c>
       <c r="B46" t="n">
-        <v>77463</v>
+        <v>82305</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5633,21 +5633,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228579</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5657,10 +5657,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>546362</v>
+        <v>546421</v>
       </c>
       <c r="R46" t="n">
-        <v>7207136</v>
+        <v>7206851</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5692,7 +5692,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5729,7 +5729,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119536367</v>
+        <v>119536364</v>
       </c>
       <c r="B47" t="n">
         <v>79608</v>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>546365</v>
+        <v>546248</v>
       </c>
       <c r="R47" t="n">
-        <v>7207145</v>
+        <v>7207265</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5841,10 +5841,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119536978</v>
+        <v>119536523</v>
       </c>
       <c r="B48" t="n">
-        <v>78526</v>
+        <v>96862</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5853,25 +5853,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>546304</v>
+        <v>546346</v>
       </c>
       <c r="R48" t="n">
-        <v>7207241</v>
+        <v>7207114</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5953,7 +5953,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119536990</v>
+        <v>119536981</v>
       </c>
       <c r="B49" t="n">
         <v>78526</v>
@@ -5993,10 +5993,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>546421</v>
+        <v>546348</v>
       </c>
       <c r="R49" t="n">
-        <v>7206848</v>
+        <v>7207126</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6065,10 +6065,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119536689</v>
+        <v>119536369</v>
       </c>
       <c r="B50" t="n">
-        <v>79643</v>
+        <v>79608</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6077,25 +6077,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6105,10 +6105,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>546346</v>
+        <v>546326</v>
       </c>
       <c r="R50" t="n">
-        <v>7207122</v>
+        <v>7207066</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 28687-2024 artfynd.xlsx
+++ b/artfynd/A 28687-2024 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119536477</v>
+        <v>119536975</v>
       </c>
       <c r="B7" t="n">
-        <v>74643</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546332</v>
+        <v>546239</v>
       </c>
       <c r="R7" t="n">
-        <v>7207014</v>
+        <v>7207276</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119536975</v>
+        <v>119536477</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>74643</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546239</v>
+        <v>546332</v>
       </c>
       <c r="R8" t="n">
-        <v>7207276</v>
+        <v>7207014</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119536047</v>
+        <v>119536622</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>94311</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,43 +1695,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546331</v>
+        <v>546344</v>
       </c>
       <c r="R11" t="n">
-        <v>7207021</v>
+        <v>7207094</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119536622</v>
+        <v>119537116</v>
       </c>
       <c r="B12" t="n">
-        <v>94311</v>
+        <v>86878</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,25 +1807,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546344</v>
+        <v>546360</v>
       </c>
       <c r="R12" t="n">
-        <v>7207094</v>
+        <v>7206982</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1875,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119537116</v>
+        <v>119536047</v>
       </c>
       <c r="B13" t="n">
-        <v>86878</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,34 +1923,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546360</v>
+        <v>546331</v>
       </c>
       <c r="R13" t="n">
-        <v>7206982</v>
+        <v>7207021</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2136,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119536368</v>
+        <v>119536992</v>
       </c>
       <c r="B15" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,21 +2152,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546348</v>
+        <v>546442</v>
       </c>
       <c r="R15" t="n">
-        <v>7207126</v>
+        <v>7206832</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119536992</v>
+        <v>119536368</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,21 +2264,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546442</v>
+        <v>546348</v>
       </c>
       <c r="R16" t="n">
-        <v>7206832</v>
+        <v>7207126</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2808,10 +2808,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119536991</v>
+        <v>119536689</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>79643</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2820,25 +2820,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546459</v>
+        <v>546346</v>
       </c>
       <c r="R21" t="n">
-        <v>7206834</v>
+        <v>7207122</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2920,10 +2920,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119536979</v>
+        <v>119536281</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2932,25 +2932,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>546364</v>
+        <v>546344</v>
       </c>
       <c r="R22" t="n">
-        <v>7207146</v>
+        <v>7207127</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3032,7 +3032,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119536983</v>
+        <v>119536991</v>
       </c>
       <c r="B23" t="n">
         <v>78526</v>
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>546349</v>
+        <v>546459</v>
       </c>
       <c r="R23" t="n">
-        <v>7207094</v>
+        <v>7206834</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3144,10 +3144,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119536689</v>
+        <v>119536979</v>
       </c>
       <c r="B24" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3156,25 +3156,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>546346</v>
+        <v>546364</v>
       </c>
       <c r="R24" t="n">
-        <v>7207122</v>
+        <v>7207146</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3256,10 +3256,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119536281</v>
+        <v>119536983</v>
       </c>
       <c r="B25" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3268,25 +3268,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>546344</v>
+        <v>546349</v>
       </c>
       <c r="R25" t="n">
-        <v>7207127</v>
+        <v>7207094</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4376,10 +4376,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119536795</v>
+        <v>119536278</v>
       </c>
       <c r="B35" t="n">
-        <v>90576</v>
+        <v>79636</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4388,25 +4388,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4416,10 +4416,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>546329</v>
+        <v>546304</v>
       </c>
       <c r="R35" t="n">
-        <v>7207211</v>
+        <v>7207242</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4488,10 +4488,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119536977</v>
+        <v>119536795</v>
       </c>
       <c r="B36" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4504,21 +4504,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>546290</v>
+        <v>546329</v>
       </c>
       <c r="R36" t="n">
-        <v>7207241</v>
+        <v>7207211</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4600,10 +4600,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119536278</v>
+        <v>119536977</v>
       </c>
       <c r="B37" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4612,25 +4612,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4640,10 +4640,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>546304</v>
+        <v>546290</v>
       </c>
       <c r="R37" t="n">
-        <v>7207242</v>
+        <v>7207241</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 28687-2024 artfynd.xlsx
+++ b/artfynd/A 28687-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119537144</v>
+        <v>119536295</v>
       </c>
       <c r="B2" t="n">
-        <v>74630</v>
+        <v>97928</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546388</v>
+        <v>546393</v>
       </c>
       <c r="R2" t="n">
-        <v>7206925</v>
+        <v>7206921</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119536987</v>
+        <v>119536984</v>
       </c>
       <c r="B3" t="n">
         <v>78526</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546333</v>
+        <v>546325</v>
       </c>
       <c r="R3" t="n">
-        <v>7207020</v>
+        <v>7207065</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119535975</v>
+        <v>119536988</v>
       </c>
       <c r="B4" t="n">
-        <v>74638</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546362</v>
+        <v>546361</v>
       </c>
       <c r="R4" t="n">
-        <v>7207136</v>
+        <v>7206982</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119536302</v>
+        <v>119536367</v>
       </c>
       <c r="B5" t="n">
-        <v>77866</v>
+        <v>79608</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6443</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546461</v>
+        <v>546365</v>
       </c>
       <c r="R5" t="n">
-        <v>7206830</v>
+        <v>7207145</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119536475</v>
+        <v>119536366</v>
       </c>
       <c r="B6" t="n">
-        <v>74643</v>
+        <v>79608</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546250</v>
+        <v>546346</v>
       </c>
       <c r="R6" t="n">
-        <v>7207262</v>
+        <v>7207178</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119536975</v>
+        <v>119537039</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546239</v>
+        <v>546421</v>
       </c>
       <c r="R7" t="n">
-        <v>7207276</v>
+        <v>7206851</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119536477</v>
+        <v>119535973</v>
       </c>
       <c r="B8" t="n">
-        <v>74643</v>
+        <v>74638</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546332</v>
+        <v>546265</v>
       </c>
       <c r="R8" t="n">
-        <v>7207014</v>
+        <v>7207255</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119537038</v>
+        <v>119535975</v>
       </c>
       <c r="B9" t="n">
-        <v>82305</v>
+        <v>74638</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546336</v>
+        <v>546362</v>
       </c>
       <c r="R9" t="n">
-        <v>7207063</v>
+        <v>7207136</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,7 +1571,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119535976</v>
+        <v>119535974</v>
       </c>
       <c r="B10" t="n">
         <v>74638</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546348</v>
+        <v>546291</v>
       </c>
       <c r="R10" t="n">
-        <v>7207093</v>
+        <v>7207241</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119536622</v>
+        <v>119536281</v>
       </c>
       <c r="B11" t="n">
-        <v>94311</v>
+        <v>79636</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1726,7 +1726,7 @@
         <v>546344</v>
       </c>
       <c r="R11" t="n">
-        <v>7207094</v>
+        <v>7207127</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119537116</v>
+        <v>119536371</v>
       </c>
       <c r="B12" t="n">
-        <v>86878</v>
+        <v>79608</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546360</v>
+        <v>546410</v>
       </c>
       <c r="R12" t="n">
-        <v>7206982</v>
+        <v>7206846</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119536047</v>
+        <v>119537116</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>86878</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,39 +1923,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546331</v>
+        <v>546360</v>
       </c>
       <c r="R13" t="n">
-        <v>7207021</v>
+        <v>7206982</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1987,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119536779</v>
+        <v>119536302</v>
       </c>
       <c r="B14" t="n">
-        <v>74622</v>
+        <v>77866</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6439</v>
+        <v>6443</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546292</v>
+        <v>546461</v>
       </c>
       <c r="R14" t="n">
-        <v>7207246</v>
+        <v>7206830</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2099,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119536992</v>
+        <v>119535976</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546442</v>
+        <v>546348</v>
       </c>
       <c r="R15" t="n">
-        <v>7206832</v>
+        <v>7207093</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2211,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119536368</v>
+        <v>119536700</v>
       </c>
       <c r="B16" t="n">
-        <v>79608</v>
+        <v>77463</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,21 +2259,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>546348</v>
+        <v>546362</v>
       </c>
       <c r="R16" t="n">
-        <v>7207126</v>
+        <v>7207136</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2360,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119536990</v>
+        <v>119536479</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>74643</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2376,21 +2371,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2400,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546421</v>
+        <v>546383</v>
       </c>
       <c r="R17" t="n">
-        <v>7206848</v>
+        <v>7206925</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2435,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2445,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119535973</v>
+        <v>119536975</v>
       </c>
       <c r="B18" t="n">
-        <v>74638</v>
+        <v>78526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2488,21 +2483,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546265</v>
+        <v>546239</v>
       </c>
       <c r="R18" t="n">
-        <v>7207255</v>
+        <v>7207276</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2547,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2584,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119536279</v>
+        <v>119536980</v>
       </c>
       <c r="B19" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2596,25 +2591,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2624,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>546347</v>
+        <v>546362</v>
       </c>
       <c r="R19" t="n">
-        <v>7207179</v>
+        <v>7207137</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2659,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119536700</v>
+        <v>119536992</v>
       </c>
       <c r="B20" t="n">
-        <v>77463</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2712,21 +2707,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2736,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546362</v>
+        <v>546442</v>
       </c>
       <c r="R20" t="n">
-        <v>7207136</v>
+        <v>7206832</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2771,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2781,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2808,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119536689</v>
+        <v>119536981</v>
       </c>
       <c r="B21" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2820,25 +2815,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2848,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>546346</v>
+        <v>546348</v>
       </c>
       <c r="R21" t="n">
-        <v>7207122</v>
+        <v>7207126</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2883,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2893,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2920,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119536281</v>
+        <v>119536622</v>
       </c>
       <c r="B22" t="n">
-        <v>79636</v>
+        <v>94311</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2936,21 +2931,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>2809</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2963,7 +2958,7 @@
         <v>546344</v>
       </c>
       <c r="R22" t="n">
-        <v>7207127</v>
+        <v>7207094</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2995,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3005,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3032,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119536991</v>
+        <v>119536523</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>96862</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3044,25 +3039,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3072,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>546459</v>
+        <v>546346</v>
       </c>
       <c r="R23" t="n">
-        <v>7206834</v>
+        <v>7207114</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3107,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3117,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3144,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119536979</v>
+        <v>119536365</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3160,21 +3155,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3184,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>546364</v>
+        <v>546304</v>
       </c>
       <c r="R24" t="n">
-        <v>7207146</v>
+        <v>7207242</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3219,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3229,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3256,7 +3251,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119536983</v>
+        <v>119536977</v>
       </c>
       <c r="B25" t="n">
         <v>78526</v>
@@ -3296,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>546349</v>
+        <v>546290</v>
       </c>
       <c r="R25" t="n">
-        <v>7207094</v>
+        <v>7207241</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3331,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3341,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3368,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119536280</v>
+        <v>119536989</v>
       </c>
       <c r="B26" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3380,25 +3375,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3408,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>546364</v>
+        <v>546388</v>
       </c>
       <c r="R26" t="n">
-        <v>7207145</v>
+        <v>7206925</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3443,7 +3438,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3453,7 +3448,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3480,10 +3475,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119536479</v>
+        <v>119536979</v>
       </c>
       <c r="B27" t="n">
-        <v>74643</v>
+        <v>78526</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3496,21 +3491,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3520,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>546383</v>
+        <v>546364</v>
       </c>
       <c r="R27" t="n">
-        <v>7206925</v>
+        <v>7207146</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3555,7 +3550,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3565,7 +3560,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3592,10 +3587,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119536980</v>
+        <v>119536795</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3608,21 +3603,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3632,10 +3627,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>546362</v>
+        <v>546329</v>
       </c>
       <c r="R28" t="n">
-        <v>7207137</v>
+        <v>7207211</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3667,7 +3662,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3677,7 +3672,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3704,10 +3699,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119536988</v>
+        <v>119536369</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3720,21 +3715,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3744,10 +3739,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>546361</v>
+        <v>546326</v>
       </c>
       <c r="R29" t="n">
-        <v>7206982</v>
+        <v>7207066</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3779,7 +3774,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3789,7 +3784,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3816,10 +3811,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119536367</v>
+        <v>119536978</v>
       </c>
       <c r="B30" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3832,21 +3827,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3856,10 +3851,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>546365</v>
+        <v>546304</v>
       </c>
       <c r="R30" t="n">
-        <v>7207145</v>
+        <v>7207241</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3891,7 +3886,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3901,7 +3896,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3928,10 +3923,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119536365</v>
+        <v>119536475</v>
       </c>
       <c r="B31" t="n">
-        <v>79608</v>
+        <v>74643</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3944,21 +3939,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3968,10 +3963,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>546304</v>
+        <v>546250</v>
       </c>
       <c r="R31" t="n">
-        <v>7207242</v>
+        <v>7207262</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4003,7 +3998,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4013,7 +4008,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4040,10 +4035,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119537037</v>
+        <v>119536987</v>
       </c>
       <c r="B32" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4056,21 +4051,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4080,10 +4075,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>546290</v>
+        <v>546333</v>
       </c>
       <c r="R32" t="n">
-        <v>7207239</v>
+        <v>7207020</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4115,7 +4110,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4125,7 +4120,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4152,7 +4147,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119536989</v>
+        <v>119536976</v>
       </c>
       <c r="B33" t="n">
         <v>78526</v>
@@ -4192,10 +4187,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>546388</v>
+        <v>546262</v>
       </c>
       <c r="R33" t="n">
-        <v>7206925</v>
+        <v>7207258</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4227,7 +4222,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4237,7 +4232,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4264,10 +4259,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119536978</v>
+        <v>119537144</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
+        <v>74630</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4280,21 +4275,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4304,10 +4299,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>546304</v>
+        <v>546388</v>
       </c>
       <c r="R34" t="n">
-        <v>7207241</v>
+        <v>7206925</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4339,7 +4334,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4349,7 +4344,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4376,10 +4371,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119536278</v>
+        <v>119536109</v>
       </c>
       <c r="B35" t="n">
-        <v>79636</v>
+        <v>57463</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4388,38 +4383,47 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>546304</v>
+        <v>546249</v>
       </c>
       <c r="R35" t="n">
-        <v>7207242</v>
+        <v>7207263</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4451,7 +4455,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4461,7 +4465,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4488,10 +4492,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119536795</v>
+        <v>119537037</v>
       </c>
       <c r="B36" t="n">
-        <v>90576</v>
+        <v>82305</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4504,21 +4508,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4528,10 +4532,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>546329</v>
+        <v>546290</v>
       </c>
       <c r="R36" t="n">
-        <v>7207211</v>
+        <v>7207239</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4563,7 +4567,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4573,7 +4577,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4600,10 +4604,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119536977</v>
+        <v>119536279</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4612,25 +4616,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4640,10 +4644,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>546290</v>
+        <v>546347</v>
       </c>
       <c r="R37" t="n">
-        <v>7207241</v>
+        <v>7207179</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4675,7 +4679,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4685,7 +4689,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4712,10 +4716,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119536976</v>
+        <v>119536779</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>74622</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4724,25 +4728,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4752,10 +4756,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>546262</v>
+        <v>546292</v>
       </c>
       <c r="R38" t="n">
-        <v>7207258</v>
+        <v>7207246</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4787,7 +4791,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4797,7 +4801,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4824,10 +4828,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119536371</v>
+        <v>119536047</v>
       </c>
       <c r="B39" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4840,34 +4844,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>546410</v>
+        <v>546331</v>
       </c>
       <c r="R39" t="n">
-        <v>7206846</v>
+        <v>7207021</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4899,7 +4908,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4909,7 +4918,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4936,10 +4945,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119535974</v>
+        <v>119537038</v>
       </c>
       <c r="B40" t="n">
-        <v>74638</v>
+        <v>82305</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4952,21 +4961,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4976,10 +4985,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>546291</v>
+        <v>546336</v>
       </c>
       <c r="R40" t="n">
-        <v>7207241</v>
+        <v>7207063</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5011,7 +5020,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5021,7 +5030,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5048,10 +5057,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119536109</v>
+        <v>119536477</v>
       </c>
       <c r="B41" t="n">
-        <v>57463</v>
+        <v>74643</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5064,43 +5073,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>1467</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Luspberget, Fatsjöluspen, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>546249</v>
+        <v>546332</v>
       </c>
       <c r="R41" t="n">
-        <v>7207263</v>
+        <v>7207014</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5169,10 +5169,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119536366</v>
+        <v>119536986</v>
       </c>
       <c r="B42" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5185,21 +5185,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5209,10 +5209,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>546346</v>
+        <v>546326</v>
       </c>
       <c r="R42" t="n">
-        <v>7207178</v>
+        <v>7207041</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5281,7 +5281,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119536984</v>
+        <v>119536990</v>
       </c>
       <c r="B43" t="n">
         <v>78526</v>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>546325</v>
+        <v>546421</v>
       </c>
       <c r="R43" t="n">
-        <v>7207065</v>
+        <v>7206848</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5393,10 +5393,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119536986</v>
+        <v>119536278</v>
       </c>
       <c r="B44" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5405,25 +5405,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5433,10 +5433,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>546326</v>
+        <v>546304</v>
       </c>
       <c r="R44" t="n">
-        <v>7207041</v>
+        <v>7207242</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5468,7 +5468,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5505,10 +5505,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119536295</v>
+        <v>119536368</v>
       </c>
       <c r="B45" t="n">
-        <v>97928</v>
+        <v>79608</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5517,25 +5517,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5545,10 +5545,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>546393</v>
+        <v>546348</v>
       </c>
       <c r="R45" t="n">
-        <v>7206921</v>
+        <v>7207126</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5617,10 +5617,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119537039</v>
+        <v>119536364</v>
       </c>
       <c r="B46" t="n">
-        <v>82305</v>
+        <v>79608</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5633,21 +5633,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5657,10 +5657,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>546421</v>
+        <v>546248</v>
       </c>
       <c r="R46" t="n">
-        <v>7206851</v>
+        <v>7207265</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5692,7 +5692,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5729,10 +5729,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119536364</v>
+        <v>119536983</v>
       </c>
       <c r="B47" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5745,21 +5745,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>546248</v>
+        <v>546349</v>
       </c>
       <c r="R47" t="n">
-        <v>7207265</v>
+        <v>7207094</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5841,10 +5841,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119536523</v>
+        <v>119536991</v>
       </c>
       <c r="B48" t="n">
-        <v>96862</v>
+        <v>78526</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5853,25 +5853,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>546346</v>
+        <v>546459</v>
       </c>
       <c r="R48" t="n">
-        <v>7207114</v>
+        <v>7206834</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5953,10 +5953,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119536981</v>
+        <v>119536689</v>
       </c>
       <c r="B49" t="n">
-        <v>78526</v>
+        <v>79643</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5965,25 +5965,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5993,10 +5993,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>546348</v>
+        <v>546346</v>
       </c>
       <c r="R49" t="n">
-        <v>7207126</v>
+        <v>7207122</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6065,10 +6065,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119536369</v>
+        <v>119536280</v>
       </c>
       <c r="B50" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6077,25 +6077,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6105,10 +6105,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>546326</v>
+        <v>546364</v>
       </c>
       <c r="R50" t="n">
-        <v>7207066</v>
+        <v>7207145</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD50" t="b">
